--- a/event_registration_forms/006_industry_conference_registration_form--event_registration_forms.xlsx
+++ b/event_registration_forms/006_industry_conference_registration_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'credit-card',_'label':_'credit_card',_'hint':_none,_'type':_'select_one',_'options':_[]}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'credit-card', 'label': 'Credit Card', 'hint': None, 'type': 'select_one', 'options': []}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'bank-transfer',_'label':_'bank_transfer',_'hint':_none,_'type':_'select_one',_'options':_[]}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'bank-transfer', 'label': 'Bank Transfer', 'hint': None, 'type': 'select_one', 'options': []}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'cash',_'label':_'cash',_'hint':_none,_'type':_'select_one',_'options':_[]}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'cash', 'label': 'Cash', 'hint': None, 'type': 'select_one', 'options': []}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'attendee-1',_'label':_'attendee_1',_'hint':_none,_'type':_'select_multiple',_'options':_[]}</t>
+          <t>attendee_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'attendee-1', 'label': 'Attendee 1', 'hint': None, 'type': 'select_multiple', 'options': []}</t>
+          <t>Attendee 1</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'attendee-2',_'label':_'attendee_2',_'hint':_none,_'type':_'select_multiple',_'options':_[]}</t>
+          <t>attendee_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'attendee-2', 'label': 'Attendee 2', 'hint': None, 'type': 'select_multiple', 'options': []}</t>
+          <t>Attendee 2</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'attendee-3',_'label':_'attendee_3',_'hint':_none,_'type':_'select_multiple',_'options':_[]}</t>
+          <t>attendee_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'attendee-3', 'label': 'Attendee 3', 'hint': None, 'type': 'select_multiple', 'options': []}</t>
+          <t>Attendee 3</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pending',_'label':_'pending',_'hint':_none,_'type':_'select_one',_'options':_[]}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'pending', 'label': 'Pending', 'hint': None, 'type': 'select_one', 'options': []}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'paid',_'label':_'paid',_'hint':_none,_'type':_'select_one',_'options':_[]}</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'paid', 'label': 'Paid', 'hint': None, 'type': 'select_one', 'options': []}</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'credit-card',_'label':_'credit_card',_'hint':_none,_'type':_'select_one',_'options':_[]}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'credit-card', 'label': 'Credit Card', 'hint': None, 'type': 'select_one', 'options': []}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'bank-transfer',_'label':_'bank_transfer',_'hint':_none,_'type':_'select_one',_'options':_[]}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'bank-transfer', 'label': 'Bank Transfer', 'hint': None, 'type': 'select_one', 'options': []}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'cash',_'label':_'cash',_'hint':_none,_'type':_'select_one',_'options':_[]}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'cash', 'label': 'Cash', 'hint': None, 'type': 'select_one', 'options': []}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
